--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_27.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:M139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4565 +469,6240 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:57.099</t>
+          <t>2026-05-29 09:47:19.095</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779509272479</v>
+        <v>1780022837732</v>
       </c>
       <c r="C2" t="n">
-        <v>88776</v>
+        <v>79013</v>
       </c>
       <c r="D2" t="n">
-        <v>110.27</v>
+        <v>442.83</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="G2" t="n">
-        <v>128.24</v>
+        <v>344.72</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1362</v>
+      </c>
+      <c r="L2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.313</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:57.110</t>
+          <t>2026-05-29 09:47:19.097</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779509272681</v>
+        <v>1780022837932</v>
       </c>
       <c r="C3" t="n">
-        <v>88981</v>
+        <v>78847</v>
       </c>
       <c r="D3" t="n">
-        <v>309.76</v>
+        <v>254.69</v>
       </c>
       <c r="E3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>499</v>
+      </c>
+      <c r="G3" t="n">
+        <v>344.72</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1164</v>
+      </c>
+      <c r="L3" t="n">
         <v>95</v>
       </c>
-      <c r="F3" t="n">
-        <v>483</v>
-      </c>
-      <c r="G3" t="n">
-        <v>128.24</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="M3" t="n">
+        <v>1.229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:57.357</t>
+          <t>2026-05-29 09:47:19.098</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779509272882</v>
+        <v>1780022838132</v>
       </c>
       <c r="C4" t="n">
-        <v>89095</v>
+        <v>78734</v>
       </c>
       <c r="D4" t="n">
-        <v>408.27</v>
+        <v>128.95</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F4" t="n">
-        <v>1309</v>
+        <v>499</v>
       </c>
       <c r="G4" t="n">
-        <v>241.22</v>
+        <v>344.72</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K4" t="n">
+        <v>965</v>
+      </c>
+      <c r="L4" t="n">
+        <v>105</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.971</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:57.359</t>
+          <t>2026-05-29 09:47:19.099</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779509273083</v>
+        <v>1780022838332</v>
       </c>
       <c r="C5" t="n">
-        <v>88801</v>
+        <v>78767</v>
       </c>
       <c r="D5" t="n">
-        <v>93.86</v>
+        <v>155.5</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F5" t="n">
-        <v>1309</v>
+        <v>499</v>
       </c>
       <c r="G5" t="n">
-        <v>241.22</v>
+        <v>344.72</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>766</v>
+      </c>
+      <c r="L5" t="n">
+        <v>105</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.091</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:57.588</t>
+          <t>2026-05-29 09:47:19.690</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779509273285</v>
+        <v>1780022838532</v>
       </c>
       <c r="C6" t="n">
-        <v>89163</v>
+        <v>78759</v>
       </c>
       <c r="D6" t="n">
-        <v>451.16</v>
+        <v>139.73</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>1309</v>
+        <v>499</v>
       </c>
       <c r="G6" t="n">
-        <v>241.22</v>
+        <v>344.72</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1155</v>
+      </c>
+      <c r="L6" t="n">
+        <v>107</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.302</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:57.590</t>
+          <t>2026-05-29 09:47:19.691</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779509273486</v>
+        <v>1780022838732</v>
       </c>
       <c r="C7" t="n">
-        <v>89224</v>
+        <v>78910</v>
       </c>
       <c r="D7" t="n">
-        <v>489.6</v>
+        <v>283.74</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F7" t="n">
-        <v>543</v>
+        <v>499</v>
       </c>
       <c r="G7" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>958</v>
+      </c>
+      <c r="L7" t="n">
+        <v>105</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:58.099</t>
+          <t>2026-05-29 09:47:21.268</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779509273687</v>
+        <v>1780022838951</v>
       </c>
       <c r="C8" t="n">
-        <v>88907</v>
+        <v>78922</v>
       </c>
       <c r="D8" t="n">
-        <v>148.12</v>
+        <v>281.56</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>543</v>
+        <v>2818</v>
       </c>
       <c r="G8" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2315</v>
+      </c>
+      <c r="L8" t="n">
+        <v>117</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.093</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:58.361</t>
+          <t>2026-05-29 09:47:21.269</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779509273889</v>
+        <v>1780022839151</v>
       </c>
       <c r="C9" t="n">
-        <v>88792</v>
+        <v>78995</v>
       </c>
       <c r="D9" t="n">
-        <v>25.72</v>
+        <v>340.48</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>543</v>
+        <v>2818</v>
       </c>
       <c r="G9" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2117</v>
+      </c>
+      <c r="L9" t="n">
+        <v>107</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.973</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:58.363</t>
+          <t>2026-05-29 09:47:21.296</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779509274090</v>
+        <v>1780022839351</v>
       </c>
       <c r="C10" t="n">
-        <v>88980</v>
+        <v>79229</v>
       </c>
       <c r="D10" t="n">
-        <v>212.43</v>
+        <v>557.45</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F10" t="n">
-        <v>543</v>
+        <v>2818</v>
       </c>
       <c r="G10" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1944</v>
+      </c>
+      <c r="L10" t="n">
+        <v>112</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.096</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:58.720</t>
+          <t>2026-05-29 09:47:21.297</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779509274292</v>
+        <v>1780022839551</v>
       </c>
       <c r="C11" t="n">
-        <v>88417</v>
+        <v>79055</v>
       </c>
       <c r="D11" t="n">
-        <v>-361.19</v>
+        <v>355.58</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>543</v>
+        <v>2818</v>
       </c>
       <c r="G11" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1746</v>
+      </c>
+      <c r="L11" t="n">
+        <v>115</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.793</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:58.966</t>
+          <t>2026-05-29 09:47:21.298</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779509274493</v>
+        <v>1780022839751</v>
       </c>
       <c r="C12" t="n">
-        <v>88522</v>
+        <v>78780</v>
       </c>
       <c r="D12" t="n">
-        <v>-238.13</v>
+        <v>62.8</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>543</v>
+        <v>2818</v>
       </c>
       <c r="G12" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1547</v>
+      </c>
+      <c r="L12" t="n">
+        <v>106</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:58.972</t>
+          <t>2026-05-29 09:47:21.307</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779509274694</v>
+        <v>1780022839951</v>
       </c>
       <c r="C13" t="n">
-        <v>88615</v>
+        <v>78521</v>
       </c>
       <c r="D13" t="n">
-        <v>-133.22</v>
+        <v>-199.34</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F13" t="n">
-        <v>543</v>
+        <v>2818</v>
       </c>
       <c r="G13" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1355</v>
+      </c>
+      <c r="L13" t="n">
+        <v>113</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.982</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:59.250</t>
+          <t>2026-05-29 09:47:21.309</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779509274896</v>
+        <v>1780022840151</v>
       </c>
       <c r="C14" t="n">
-        <v>88409</v>
+        <v>78708</v>
       </c>
       <c r="D14" t="n">
-        <v>-332.56</v>
+        <v>-2.37</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>543</v>
+        <v>2818</v>
       </c>
       <c r="G14" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L14" t="n">
+        <v>113</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.989</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:59.258</t>
+          <t>2026-05-29 09:47:21.609</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779509275097</v>
+        <v>1780022840370</v>
       </c>
       <c r="C15" t="n">
-        <v>88285</v>
+        <v>78956</v>
       </c>
       <c r="D15" t="n">
-        <v>-439.93</v>
+        <v>245.75</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
-        <v>543</v>
+        <v>2818</v>
       </c>
       <c r="G15" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1238</v>
+      </c>
+      <c r="L15" t="n">
+        <v>108</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.177</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:59.259</t>
+          <t>2026-05-29 09:47:21.624</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779509275298</v>
+        <v>1780022840570</v>
       </c>
       <c r="C16" t="n">
-        <v>88384</v>
+        <v>78591</v>
       </c>
       <c r="D16" t="n">
-        <v>-318.94</v>
+        <v>-131.54</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F16" t="n">
-        <v>543</v>
+        <v>1619</v>
       </c>
       <c r="G16" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J16" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1053</v>
+      </c>
+      <c r="L16" t="n">
+        <v>117</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.717</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:59.727</t>
+          <t>2026-05-29 09:47:22.909</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779509275500</v>
+        <v>1780022840770</v>
       </c>
       <c r="C17" t="n">
-        <v>88521</v>
+        <v>78996</v>
       </c>
       <c r="D17" t="n">
-        <v>-165.99</v>
+        <v>280.04</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F17" t="n">
-        <v>543</v>
+        <v>1619</v>
       </c>
       <c r="G17" t="n">
-        <v>242.81</v>
+        <v>344.72</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J17" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2138</v>
+      </c>
+      <c r="L17" t="n">
+        <v>116</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.151</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:59.996</t>
+          <t>2026-05-29 09:47:22.911</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779509275701</v>
+        <v>1780022840970</v>
       </c>
       <c r="C18" t="n">
-        <v>88100</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="n">
-        <v>-578.6900000000001</v>
+        <v>311.04</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="F18" t="n">
-        <v>2175</v>
+        <v>360</v>
       </c>
       <c r="G18" t="n">
-        <v>242.81</v>
+        <v>374.35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="L18" t="n">
+        <v>108</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:00.319</t>
+          <t>2026-05-29 09:47:22.921</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779509275902</v>
+        <v>1780022841170</v>
       </c>
       <c r="C19" t="n">
-        <v>88251</v>
+        <v>79154</v>
       </c>
       <c r="D19" t="n">
-        <v>-398.76</v>
+        <v>408.48</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="F19" t="n">
-        <v>2175</v>
+        <v>360</v>
       </c>
       <c r="G19" t="n">
-        <v>242.81</v>
+        <v>374.35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1749</v>
+      </c>
+      <c r="L19" t="n">
+        <v>109</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.416</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:00.320</t>
+          <t>2026-05-29 09:47:22.950</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779509276104</v>
+        <v>1780022841370</v>
       </c>
       <c r="C20" t="n">
-        <v>88420</v>
+        <v>79003</v>
       </c>
       <c r="D20" t="n">
-        <v>-209.82</v>
+        <v>237.06</v>
       </c>
       <c r="E20" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="F20" t="n">
-        <v>2175</v>
+        <v>360</v>
       </c>
       <c r="G20" t="n">
-        <v>242.81</v>
+        <v>374.35</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1579</v>
+      </c>
+      <c r="L20" t="n">
+        <v>107</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.876</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:00.638</t>
+          <t>2026-05-29 09:47:23.275</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779509276305</v>
+        <v>1780022841570</v>
       </c>
       <c r="C21" t="n">
-        <v>87920</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="n">
-        <v>-699.33</v>
+        <v>245.21</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="F21" t="n">
-        <v>604</v>
+        <v>360</v>
       </c>
       <c r="G21" t="n">
-        <v>244.46</v>
+        <v>374.35</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1704</v>
+      </c>
+      <c r="L21" t="n">
+        <v>122</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.839</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:00.918</t>
+          <t>2026-05-29 09:47:23.280</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779509276506</v>
+        <v>1780022841770</v>
       </c>
       <c r="C22" t="n">
-        <v>88081</v>
+        <v>79142</v>
       </c>
       <c r="D22" t="n">
-        <v>-503.36</v>
+        <v>351.95</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F22" t="n">
-        <v>604</v>
+        <v>840</v>
       </c>
       <c r="G22" t="n">
-        <v>244.46</v>
+        <v>332.25</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1509</v>
+      </c>
+      <c r="L22" t="n">
+        <v>108</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.604</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:00.943</t>
+          <t>2026-05-29 09:47:23.282</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779509276708</v>
+        <v>1780022841989</v>
       </c>
       <c r="C23" t="n">
-        <v>88187</v>
+        <v>78762</v>
       </c>
       <c r="D23" t="n">
-        <v>-372.19</v>
+        <v>-45.65</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F23" t="n">
-        <v>604</v>
+        <v>840</v>
       </c>
       <c r="G23" t="n">
-        <v>244.46</v>
+        <v>332.25</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1292</v>
+      </c>
+      <c r="L23" t="n">
+        <v>108</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.585</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:01.400</t>
+          <t>2026-05-29 09:47:23.858</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779509276909</v>
+        <v>1780022842189</v>
       </c>
       <c r="C24" t="n">
-        <v>87966</v>
+        <v>78524</v>
       </c>
       <c r="D24" t="n">
-        <v>-574.58</v>
+        <v>-281.37</v>
       </c>
       <c r="E24" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F24" t="n">
-        <v>685</v>
+        <v>840</v>
       </c>
       <c r="G24" t="n">
-        <v>241.79</v>
+        <v>332.25</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1668</v>
+      </c>
+      <c r="L24" t="n">
+        <v>110</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.495</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:01.407</t>
+          <t>2026-05-29 09:47:23.859</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779509277110</v>
+        <v>1780022842389</v>
       </c>
       <c r="C25" t="n">
-        <v>87794</v>
+        <v>78443</v>
       </c>
       <c r="D25" t="n">
-        <v>-717.85</v>
+        <v>-348.3</v>
       </c>
       <c r="E25" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F25" t="n">
-        <v>685</v>
+        <v>840</v>
       </c>
       <c r="G25" t="n">
-        <v>241.79</v>
+        <v>332.25</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J25" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1469</v>
+      </c>
+      <c r="L25" t="n">
+        <v>110</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:01.730</t>
+          <t>2026-05-29 09:47:23.901</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779509277312</v>
+        <v>1780022842589</v>
       </c>
       <c r="C26" t="n">
-        <v>87822</v>
+        <v>78169</v>
       </c>
       <c r="D26" t="n">
-        <v>-653.96</v>
+        <v>-604.89</v>
       </c>
       <c r="E26" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F26" t="n">
-        <v>685</v>
+        <v>840</v>
       </c>
       <c r="G26" t="n">
-        <v>241.79</v>
+        <v>332.25</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J26" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1311</v>
+      </c>
+      <c r="L26" t="n">
+        <v>112</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.853</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:01.731</t>
+          <t>2026-05-29 09:47:23.904</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779509277513</v>
+        <v>1780022842789</v>
       </c>
       <c r="C27" t="n">
-        <v>88016</v>
+        <v>78314</v>
       </c>
       <c r="D27" t="n">
-        <v>-427.26</v>
+        <v>-429.64</v>
       </c>
       <c r="E27" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F27" t="n">
-        <v>685</v>
+        <v>840</v>
       </c>
       <c r="G27" t="n">
-        <v>241.79</v>
+        <v>332.25</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1113</v>
+      </c>
+      <c r="L27" t="n">
+        <v>116</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.716</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:01.732</t>
+          <t>2026-05-29 09:47:23.907</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779509277715</v>
+        <v>1780022842989</v>
       </c>
       <c r="C28" t="n">
-        <v>87726</v>
+        <v>78712</v>
       </c>
       <c r="D28" t="n">
-        <v>-695.9</v>
+        <v>-10.16</v>
       </c>
       <c r="E28" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F28" t="n">
-        <v>805</v>
+        <v>840</v>
       </c>
       <c r="G28" t="n">
-        <v>243.26</v>
+        <v>332.25</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>917</v>
+      </c>
+      <c r="L28" t="n">
+        <v>104</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.755</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:02.329</t>
+          <t>2026-05-29 09:47:24.240</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779509277916</v>
+        <v>1780022843189</v>
       </c>
       <c r="C29" t="n">
-        <v>87979</v>
+        <v>78528</v>
       </c>
       <c r="D29" t="n">
-        <v>-408.11</v>
+        <v>-193.65</v>
       </c>
       <c r="E29" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>805</v>
+        <v>1359</v>
       </c>
       <c r="G29" t="n">
-        <v>243.26</v>
+        <v>361.99</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1050</v>
+      </c>
+      <c r="L29" t="n">
+        <v>122</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.805</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:02.620</t>
+          <t>2026-05-29 09:47:24.246</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779509278117</v>
+        <v>1780022843389</v>
       </c>
       <c r="C30" t="n">
-        <v>88197</v>
+        <v>78509</v>
       </c>
       <c r="D30" t="n">
-        <v>-169.7</v>
+        <v>-202.97</v>
       </c>
       <c r="E30" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>403</v>
+        <v>1359</v>
       </c>
       <c r="G30" t="n">
-        <v>264.34</v>
+        <v>361.99</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K30" t="n">
+        <v>857</v>
+      </c>
+      <c r="L30" t="n">
+        <v>116</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.595</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:02.622</t>
+          <t>2026-05-29 09:47:24.787</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779509278319</v>
+        <v>1780022843608</v>
       </c>
       <c r="C31" t="n">
-        <v>87989</v>
+        <v>78616</v>
       </c>
       <c r="D31" t="n">
-        <v>-369.22</v>
+        <v>-85.81999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>403</v>
+        <v>1359</v>
       </c>
       <c r="G31" t="n">
-        <v>264.34</v>
+        <v>361.99</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1177</v>
+      </c>
+      <c r="L31" t="n">
+        <v>125</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.122</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:02.946</t>
+          <t>2026-05-29 09:47:24.817</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779509278520</v>
+        <v>1780022843808</v>
       </c>
       <c r="C32" t="n">
-        <v>87694</v>
+        <v>78308</v>
       </c>
       <c r="D32" t="n">
-        <v>-645.75</v>
+        <v>-389.53</v>
       </c>
       <c r="E32" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F32" t="n">
-        <v>403</v>
+        <v>719</v>
       </c>
       <c r="G32" t="n">
-        <v>264.34</v>
+        <v>353.57</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1008</v>
+      </c>
+      <c r="L32" t="n">
+        <v>104</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.354</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:02.961</t>
+          <t>2026-05-29 09:47:25.049</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779509278721</v>
+        <v>1780022844008</v>
       </c>
       <c r="C33" t="n">
-        <v>87762</v>
+        <v>79080</v>
       </c>
       <c r="D33" t="n">
-        <v>-545.47</v>
+        <v>401.95</v>
       </c>
       <c r="E33" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F33" t="n">
-        <v>403</v>
+        <v>719</v>
       </c>
       <c r="G33" t="n">
-        <v>264.34</v>
+        <v>353.57</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1040</v>
+      </c>
+      <c r="L33" t="n">
+        <v>105</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.836</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:03.424</t>
+          <t>2026-05-29 09:47:25.078</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779509278923</v>
+        <v>1780022844208</v>
       </c>
       <c r="C34" t="n">
-        <v>87651</v>
+        <v>80310</v>
       </c>
       <c r="D34" t="n">
-        <v>-629.1900000000001</v>
+        <v>1611.85</v>
       </c>
       <c r="E34" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F34" t="n">
-        <v>403</v>
+        <v>340</v>
       </c>
       <c r="G34" t="n">
-        <v>264.34</v>
+        <v>368.83</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>869</v>
+      </c>
+      <c r="L34" t="n">
+        <v>107</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.989</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:03.775</t>
+          <t>2026-05-29 09:47:25.478</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779509279124</v>
+        <v>1780022844408</v>
       </c>
       <c r="C35" t="n">
-        <v>87440</v>
+        <v>76946</v>
       </c>
       <c r="D35" t="n">
-        <v>-808.73</v>
+        <v>-1832.74</v>
       </c>
       <c r="E35" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F35" t="n">
-        <v>403</v>
+        <v>340</v>
       </c>
       <c r="G35" t="n">
-        <v>264.34</v>
+        <v>368.83</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1069</v>
+      </c>
+      <c r="L35" t="n">
+        <v>106</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:03.788</t>
+          <t>2026-05-29 09:47:25.524</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779509279325</v>
+        <v>1780022844608</v>
       </c>
       <c r="C36" t="n">
-        <v>87700</v>
+        <v>75666</v>
       </c>
       <c r="D36" t="n">
-        <v>-508.3</v>
+        <v>-3021.11</v>
       </c>
       <c r="E36" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F36" t="n">
-        <v>403</v>
+        <v>340</v>
       </c>
       <c r="G36" t="n">
-        <v>264.34</v>
+        <v>368.83</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>915</v>
+      </c>
+      <c r="L36" t="n">
+        <v>104</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.9320000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:03.790</t>
+          <t>2026-05-29 09:47:25.863</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779509279527</v>
+        <v>1780022844808</v>
       </c>
       <c r="C37" t="n">
-        <v>88058</v>
+        <v>77801</v>
       </c>
       <c r="D37" t="n">
-        <v>-124.88</v>
+        <v>-735.05</v>
       </c>
       <c r="E37" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F37" t="n">
-        <v>1429</v>
+        <v>340</v>
       </c>
       <c r="G37" t="n">
-        <v>345.49</v>
+        <v>368.83</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1053</v>
+      </c>
+      <c r="L37" t="n">
+        <v>107</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.619</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:04.036</t>
+          <t>2026-05-29 09:47:25.885</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779509279728</v>
+        <v>1780022845008</v>
       </c>
       <c r="C38" t="n">
-        <v>87700</v>
+        <v>79354</v>
       </c>
       <c r="D38" t="n">
-        <v>-476.64</v>
+        <v>854.7</v>
       </c>
       <c r="E38" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F38" t="n">
-        <v>1429</v>
+        <v>340</v>
       </c>
       <c r="G38" t="n">
-        <v>345.49</v>
+        <v>368.83</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>876</v>
+      </c>
+      <c r="L38" t="n">
+        <v>106</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.077</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:04.037</t>
+          <t>2026-05-29 09:47:26.497</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779509279929</v>
+        <v>1780022845227</v>
       </c>
       <c r="C39" t="n">
-        <v>87813</v>
+        <v>81544</v>
       </c>
       <c r="D39" t="n">
-        <v>-339.81</v>
+        <v>3001.97</v>
       </c>
       <c r="E39" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F39" t="n">
-        <v>1429</v>
+        <v>340</v>
       </c>
       <c r="G39" t="n">
-        <v>345.49</v>
+        <v>368.83</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1268</v>
+      </c>
+      <c r="L39" t="n">
+        <v>106</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.546</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:04.401</t>
+          <t>2026-05-29 09:47:26.530</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779509280131</v>
+        <v>1780022845427</v>
       </c>
       <c r="C40" t="n">
-        <v>87947</v>
+        <v>82697</v>
       </c>
       <c r="D40" t="n">
-        <v>-188.82</v>
+        <v>4004.87</v>
       </c>
       <c r="E40" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F40" t="n">
-        <v>1429</v>
+        <v>340</v>
       </c>
       <c r="G40" t="n">
-        <v>345.49</v>
+        <v>368.83</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1102</v>
+      </c>
+      <c r="L40" t="n">
+        <v>105</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.636</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:04.402</t>
+          <t>2026-05-29 09:47:26.843</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779509280332</v>
+        <v>1780022845627</v>
       </c>
       <c r="C41" t="n">
-        <v>87950</v>
+        <v>81538</v>
       </c>
       <c r="D41" t="n">
-        <v>-176.38</v>
+        <v>2645.63</v>
       </c>
       <c r="E41" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F41" t="n">
-        <v>705</v>
+        <v>340</v>
       </c>
       <c r="G41" t="n">
-        <v>343.25</v>
+        <v>368.83</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1216</v>
+      </c>
+      <c r="L41" t="n">
+        <v>107</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.519</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:04.813</t>
+          <t>2026-05-29 09:47:26.844</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779509280534</v>
+        <v>1780022845827</v>
       </c>
       <c r="C42" t="n">
-        <v>87587</v>
+        <v>79694</v>
       </c>
       <c r="D42" t="n">
-        <v>-530.5599999999999</v>
+        <v>669.34</v>
       </c>
       <c r="E42" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F42" t="n">
-        <v>705</v>
+        <v>340</v>
       </c>
       <c r="G42" t="n">
-        <v>343.25</v>
+        <v>368.83</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1017</v>
+      </c>
+      <c r="L42" t="n">
+        <v>104</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.547</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:05.073</t>
+          <t>2026-05-29 09:47:27.097</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779509280735</v>
+        <v>1780022846027</v>
       </c>
       <c r="C43" t="n">
-        <v>87820</v>
+        <v>79477</v>
       </c>
       <c r="D43" t="n">
-        <v>-271.03</v>
+        <v>418.88</v>
       </c>
       <c r="E43" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F43" t="n">
-        <v>705</v>
+        <v>340</v>
       </c>
       <c r="G43" t="n">
-        <v>343.25</v>
+        <v>368.83</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1068</v>
+      </c>
+      <c r="L43" t="n">
+        <v>106</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:05.432</t>
+          <t>2026-05-29 09:47:27.099</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779509280936</v>
+        <v>1780022846227</v>
       </c>
       <c r="C44" t="n">
-        <v>87952</v>
+        <v>76706</v>
       </c>
       <c r="D44" t="n">
-        <v>-125.48</v>
+        <v>-2373.07</v>
       </c>
       <c r="E44" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F44" t="n">
-        <v>725</v>
+        <v>340</v>
       </c>
       <c r="G44" t="n">
-        <v>339.22</v>
+        <v>368.83</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K44" t="n">
+        <v>870</v>
+      </c>
+      <c r="L44" t="n">
+        <v>106</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.771</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:05.433</t>
+          <t>2026-05-29 09:47:27.828</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779509281138</v>
+        <v>1780022846427</v>
       </c>
       <c r="C45" t="n">
-        <v>87470</v>
+        <v>76864</v>
       </c>
       <c r="D45" t="n">
-        <v>-601.2</v>
+        <v>-2096.41</v>
       </c>
       <c r="E45" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F45" t="n">
-        <v>725</v>
+        <v>340</v>
       </c>
       <c r="G45" t="n">
-        <v>339.22</v>
+        <v>368.83</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1399</v>
+      </c>
+      <c r="L45" t="n">
+        <v>109</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.438</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:05.808</t>
+          <t>2026-05-29 09:47:27.832</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779509281339</v>
+        <v>1780022846646</v>
       </c>
       <c r="C46" t="n">
-        <v>87626</v>
+        <v>79188</v>
       </c>
       <c r="D46" t="n">
-        <v>-415.14</v>
+        <v>332.41</v>
       </c>
       <c r="E46" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F46" t="n">
-        <v>725</v>
+        <v>340</v>
       </c>
       <c r="G46" t="n">
-        <v>339.22</v>
+        <v>368.83</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1185</v>
+      </c>
+      <c r="L46" t="n">
+        <v>106</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.527</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:06.099</t>
+          <t>2026-05-29 09:47:27.833</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779509281540</v>
+        <v>1780022846846</v>
       </c>
       <c r="C47" t="n">
-        <v>87703</v>
+        <v>76496</v>
       </c>
       <c r="D47" t="n">
-        <v>-317.39</v>
+        <v>-2376.21</v>
       </c>
       <c r="E47" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F47" t="n">
-        <v>725</v>
+        <v>340</v>
       </c>
       <c r="G47" t="n">
-        <v>339.22</v>
+        <v>368.83</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K47" t="n">
+        <v>986</v>
+      </c>
+      <c r="L47" t="n">
+        <v>102</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.716</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:06.101</t>
+          <t>2026-05-29 09:47:28.123</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779509281742</v>
+        <v>1780022847046</v>
       </c>
       <c r="C48" t="n">
-        <v>87627</v>
+        <v>77773</v>
       </c>
       <c r="D48" t="n">
-        <v>-377.52</v>
+        <v>-980.4</v>
       </c>
       <c r="E48" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F48" t="n">
-        <v>725</v>
+        <v>340</v>
       </c>
       <c r="G48" t="n">
-        <v>324.87</v>
+        <v>368.83</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1077</v>
+      </c>
+      <c r="L48" t="n">
+        <v>110</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.522</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:06.339</t>
+          <t>2026-05-29 09:47:28.139</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779509281943</v>
+        <v>1780022847246</v>
       </c>
       <c r="C49" t="n">
-        <v>87467</v>
+        <v>79079</v>
       </c>
       <c r="D49" t="n">
-        <v>-518.64</v>
+        <v>374.62</v>
       </c>
       <c r="E49" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F49" t="n">
-        <v>725</v>
+        <v>340</v>
       </c>
       <c r="G49" t="n">
-        <v>324.87</v>
+        <v>368.83</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>892</v>
+      </c>
+      <c r="L49" t="n">
+        <v>107</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:06.341</t>
+          <t>2026-05-29 09:47:28.508</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779509282144</v>
+        <v>1780022847446</v>
       </c>
       <c r="C50" t="n">
-        <v>87638</v>
+        <v>79019</v>
       </c>
       <c r="D50" t="n">
-        <v>-321.71</v>
+        <v>295.89</v>
       </c>
       <c r="E50" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F50" t="n">
-        <v>725</v>
+        <v>340</v>
       </c>
       <c r="G50" t="n">
-        <v>324.87</v>
+        <v>368.83</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1061</v>
+      </c>
+      <c r="L50" t="n">
+        <v>111</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:06.695</t>
+          <t>2026-05-29 09:47:28.785</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779509282346</v>
+        <v>1780022847646</v>
       </c>
       <c r="C51" t="n">
-        <v>87741</v>
+        <v>78761</v>
       </c>
       <c r="D51" t="n">
-        <v>-202.62</v>
+        <v>23.09</v>
       </c>
       <c r="E51" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F51" t="n">
-        <v>685</v>
+        <v>340</v>
       </c>
       <c r="G51" t="n">
-        <v>270.13</v>
+        <v>368.83</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1138</v>
+      </c>
+      <c r="L51" t="n">
+        <v>105</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.084</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:06.942</t>
+          <t>2026-05-29 09:47:28.961</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779509282547</v>
+        <v>1780022847846</v>
       </c>
       <c r="C52" t="n">
-        <v>87500</v>
+        <v>80356</v>
       </c>
       <c r="D52" t="n">
-        <v>-433.49</v>
+        <v>1616.94</v>
       </c>
       <c r="E52" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F52" t="n">
-        <v>685</v>
+        <v>340</v>
       </c>
       <c r="G52" t="n">
-        <v>270.13</v>
+        <v>368.83</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1114</v>
+      </c>
+      <c r="L52" t="n">
+        <v>106</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.863</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:06.943</t>
+          <t>2026-05-29 09:47:28.962</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779509282748</v>
+        <v>1780022848065</v>
       </c>
       <c r="C53" t="n">
-        <v>87669</v>
+        <v>80893</v>
       </c>
       <c r="D53" t="n">
-        <v>-242.82</v>
+        <v>2073.09</v>
       </c>
       <c r="E53" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F53" t="n">
-        <v>685</v>
+        <v>340</v>
       </c>
       <c r="G53" t="n">
-        <v>270.13</v>
+        <v>368.83</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>896</v>
+      </c>
+      <c r="L53" t="n">
+        <v>109</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.722</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:07.362</t>
+          <t>2026-05-29 09:47:29.306</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779509282950</v>
+        <v>1780022848265</v>
       </c>
       <c r="C54" t="n">
-        <v>87815</v>
+        <v>80719</v>
       </c>
       <c r="D54" t="n">
-        <v>-84.68000000000001</v>
+        <v>1795.44</v>
       </c>
       <c r="E54" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F54" t="n">
-        <v>624</v>
+        <v>340</v>
       </c>
       <c r="G54" t="n">
-        <v>265.03</v>
+        <v>368.83</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1041</v>
+      </c>
+      <c r="L54" t="n">
+        <v>107</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:07.623</t>
+          <t>2026-05-29 09:47:29.308</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779509283151</v>
+        <v>1780022848465</v>
       </c>
       <c r="C55" t="n">
-        <v>87823</v>
+        <v>79338</v>
       </c>
       <c r="D55" t="n">
-        <v>-72.44</v>
+        <v>324.66</v>
       </c>
       <c r="E55" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F55" t="n">
-        <v>624</v>
+        <v>340</v>
       </c>
       <c r="G55" t="n">
-        <v>265.03</v>
+        <v>368.83</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>842</v>
+      </c>
+      <c r="L55" t="n">
+        <v>108</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.956</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:07.624</t>
+          <t>2026-05-29 09:47:29.869</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779509283353</v>
+        <v>1780022848665</v>
       </c>
       <c r="C56" t="n">
-        <v>87583</v>
+        <v>78491</v>
       </c>
       <c r="D56" t="n">
-        <v>-308.82</v>
+        <v>-538.5700000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F56" t="n">
-        <v>624</v>
+        <v>340</v>
       </c>
       <c r="G56" t="n">
-        <v>265.03</v>
+        <v>368.83</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1203</v>
+      </c>
+      <c r="L56" t="n">
+        <v>105</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.654</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:07.895</t>
+          <t>2026-05-29 09:47:29.870</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779509283554</v>
+        <v>1780022848865</v>
       </c>
       <c r="C57" t="n">
-        <v>87679</v>
+        <v>78805</v>
       </c>
       <c r="D57" t="n">
-        <v>-197.38</v>
+        <v>-197.64</v>
       </c>
       <c r="E57" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F57" t="n">
-        <v>624</v>
+        <v>340</v>
       </c>
       <c r="G57" t="n">
-        <v>265.03</v>
+        <v>368.83</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1005</v>
+      </c>
+      <c r="L57" t="n">
+        <v>108</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.717</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:07.942</t>
+          <t>2026-05-29 09:47:30.769</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779509283755</v>
+        <v>1780022849065</v>
       </c>
       <c r="C58" t="n">
-        <v>87858</v>
+        <v>79182</v>
       </c>
       <c r="D58" t="n">
-        <v>-8.51</v>
+        <v>189.24</v>
       </c>
       <c r="E58" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F58" t="n">
-        <v>805</v>
+        <v>340</v>
       </c>
       <c r="G58" t="n">
-        <v>261.25</v>
+        <v>368.83</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1703</v>
+      </c>
+      <c r="L58" t="n">
+        <v>110</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.738</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:08.256</t>
+          <t>2026-05-29 09:47:30.769</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779509283957</v>
+        <v>1780022849265</v>
       </c>
       <c r="C59" t="n">
-        <v>87361</v>
+        <v>78896</v>
       </c>
       <c r="D59" t="n">
-        <v>-505.09</v>
+        <v>-106.22</v>
       </c>
       <c r="E59" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F59" t="n">
-        <v>805</v>
+        <v>340</v>
       </c>
       <c r="G59" t="n">
-        <v>261.25</v>
+        <v>368.83</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1504</v>
+      </c>
+      <c r="L59" t="n">
+        <v>106</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.5679999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:08.554</t>
+          <t>2026-05-29 09:47:31.214</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779509284158</v>
+        <v>1780022849484</v>
       </c>
       <c r="C60" t="n">
-        <v>87515</v>
+        <v>78184</v>
       </c>
       <c r="D60" t="n">
-        <v>-325.83</v>
+        <v>-812.91</v>
       </c>
       <c r="E60" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F60" t="n">
-        <v>805</v>
+        <v>340</v>
       </c>
       <c r="G60" t="n">
-        <v>261.25</v>
+        <v>368.83</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1729</v>
+      </c>
+      <c r="L60" t="n">
+        <v>106</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.799</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:08.555</t>
+          <t>2026-05-29 09:47:31.223</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779509284359</v>
+        <v>1780022849684</v>
       </c>
       <c r="C61" t="n">
-        <v>87585</v>
+        <v>77123</v>
       </c>
       <c r="D61" t="n">
-        <v>-239.54</v>
+        <v>-1833.26</v>
       </c>
       <c r="E61" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F61" t="n">
-        <v>805</v>
+        <v>340</v>
       </c>
       <c r="G61" t="n">
-        <v>261.25</v>
+        <v>368.83</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1539</v>
+      </c>
+      <c r="L61" t="n">
+        <v>106</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.578</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:08.810</t>
+          <t>2026-05-29 09:47:31.232</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779509284561</v>
+        <v>1780022849884</v>
       </c>
       <c r="C62" t="n">
-        <v>87594</v>
+        <v>77079</v>
       </c>
       <c r="D62" t="n">
-        <v>-218.56</v>
+        <v>-1785.6</v>
       </c>
       <c r="E62" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F62" t="n">
-        <v>805</v>
+        <v>340</v>
       </c>
       <c r="G62" t="n">
-        <v>261.25</v>
+        <v>368.83</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1347</v>
+      </c>
+      <c r="L62" t="n">
+        <v>104</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.928</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:08.811</t>
+          <t>2026-05-29 09:47:31.246</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779509284762</v>
+        <v>1780022850084</v>
       </c>
       <c r="C63" t="n">
-        <v>87303</v>
+        <v>77081</v>
       </c>
       <c r="D63" t="n">
-        <v>-498.63</v>
+        <v>-1694.32</v>
       </c>
       <c r="E63" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F63" t="n">
-        <v>866</v>
+        <v>340</v>
       </c>
       <c r="G63" t="n">
-        <v>261.82</v>
+        <v>368.83</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1161</v>
+      </c>
+      <c r="L63" t="n">
+        <v>108</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.583</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:09.171</t>
+          <t>2026-05-29 09:47:32.558</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779509284963</v>
+        <v>1780022850284</v>
       </c>
       <c r="C64" t="n">
-        <v>87468</v>
+        <v>77147</v>
       </c>
       <c r="D64" t="n">
-        <v>-308.7</v>
+        <v>-1543.6</v>
       </c>
       <c r="E64" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F64" t="n">
-        <v>866</v>
+        <v>340</v>
       </c>
       <c r="G64" t="n">
-        <v>261.82</v>
+        <v>368.83</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2272</v>
+      </c>
+      <c r="L64" t="n">
+        <v>105</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:09.457</t>
+          <t>2026-05-29 09:47:32.559</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779509285165</v>
+        <v>1780022850484</v>
       </c>
       <c r="C65" t="n">
-        <v>87696</v>
+        <v>76380</v>
       </c>
       <c r="D65" t="n">
-        <v>-65.27</v>
+        <v>-2233.42</v>
       </c>
       <c r="E65" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F65" t="n">
-        <v>544</v>
+        <v>340</v>
       </c>
       <c r="G65" t="n">
-        <v>271.57</v>
+        <v>368.83</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J65" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2074</v>
+      </c>
+      <c r="L65" t="n">
+        <v>107</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.891</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:09.771</t>
+          <t>2026-05-29 09:47:32.560</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779509285366</v>
+        <v>1780022850684</v>
       </c>
       <c r="C66" t="n">
-        <v>87427</v>
+        <v>76932</v>
       </c>
       <c r="D66" t="n">
-        <v>-331</v>
+        <v>-1569.75</v>
       </c>
       <c r="E66" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F66" t="n">
-        <v>544</v>
+        <v>340</v>
       </c>
       <c r="G66" t="n">
-        <v>271.57</v>
+        <v>368.83</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1875</v>
+      </c>
+      <c r="L66" t="n">
+        <v>106</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:10.046</t>
+          <t>2026-05-29 09:47:32.561</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779509285568</v>
+        <v>1780022850884</v>
       </c>
       <c r="C67" t="n">
-        <v>87520</v>
+        <v>77544</v>
       </c>
       <c r="D67" t="n">
-        <v>-221.45</v>
+        <v>-879.27</v>
       </c>
       <c r="E67" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F67" t="n">
-        <v>544</v>
+        <v>340</v>
       </c>
       <c r="G67" t="n">
-        <v>271.57</v>
+        <v>368.83</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1676</v>
+      </c>
+      <c r="L67" t="n">
+        <v>110</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:10.052</t>
+          <t>2026-05-29 09:47:32.562</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779509285769</v>
+        <v>1780022851103</v>
       </c>
       <c r="C68" t="n">
-        <v>87632</v>
+        <v>76660</v>
       </c>
       <c r="D68" t="n">
-        <v>-98.38</v>
+        <v>-1719.3</v>
       </c>
       <c r="E68" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F68" t="n">
-        <v>544</v>
+        <v>340</v>
       </c>
       <c r="G68" t="n">
-        <v>271.57</v>
+        <v>368.83</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1458</v>
+      </c>
+      <c r="L68" t="n">
+        <v>105</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.9320000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:10.301</t>
+          <t>2026-05-29 09:47:32.564</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779509285970</v>
+        <v>1780022851303</v>
       </c>
       <c r="C69" t="n">
-        <v>87469</v>
+        <v>77091</v>
       </c>
       <c r="D69" t="n">
-        <v>-256.46</v>
+        <v>-1202.34</v>
       </c>
       <c r="E69" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F69" t="n">
-        <v>644</v>
+        <v>340</v>
       </c>
       <c r="G69" t="n">
-        <v>246.81</v>
+        <v>368.83</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1259</v>
+      </c>
+      <c r="L69" t="n">
+        <v>105</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.355</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:10.305</t>
+          <t>2026-05-29 09:47:32.565</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779509286172</v>
+        <v>1780022851503</v>
       </c>
       <c r="C70" t="n">
-        <v>87270</v>
+        <v>76780</v>
       </c>
       <c r="D70" t="n">
-        <v>-442.64</v>
+        <v>-1453.22</v>
       </c>
       <c r="E70" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F70" t="n">
-        <v>644</v>
+        <v>7375</v>
       </c>
       <c r="G70" t="n">
-        <v>246.81</v>
+        <v>368.83</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1061</v>
+      </c>
+      <c r="L70" t="n">
+        <v>97</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.094</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:10.579</t>
+          <t>2026-05-29 09:47:32.958</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779509286373</v>
+        <v>1780022851703</v>
       </c>
       <c r="C71" t="n">
-        <v>87349</v>
+        <v>76667</v>
       </c>
       <c r="D71" t="n">
-        <v>-341.51</v>
+        <v>-1493.56</v>
       </c>
       <c r="E71" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F71" t="n">
-        <v>644</v>
+        <v>7375</v>
       </c>
       <c r="G71" t="n">
-        <v>246.81</v>
+        <v>368.83</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J71" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1254</v>
+      </c>
+      <c r="L71" t="n">
+        <v>114</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.653</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:10.580</t>
+          <t>2026-05-29 09:47:33.024</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779509286574</v>
+        <v>1780022851903</v>
       </c>
       <c r="C72" t="n">
-        <v>87611</v>
+        <v>76821</v>
       </c>
       <c r="D72" t="n">
-        <v>-62.43</v>
+        <v>-1264.88</v>
       </c>
       <c r="E72" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F72" t="n">
-        <v>644</v>
+        <v>7375</v>
       </c>
       <c r="G72" t="n">
-        <v>246.81</v>
+        <v>368.83</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L72" t="n">
+        <v>109</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.821</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:11.442</t>
+          <t>2026-05-29 09:47:33.026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779509286776</v>
+        <v>1780022852103</v>
       </c>
       <c r="C73" t="n">
-        <v>87189</v>
+        <v>76565</v>
       </c>
       <c r="D73" t="n">
-        <v>-481.31</v>
+        <v>-1457.64</v>
       </c>
       <c r="E73" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F73" t="n">
-        <v>826</v>
+        <v>7375</v>
       </c>
       <c r="G73" t="n">
-        <v>98.31</v>
+        <v>368.83</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K73" t="n">
+        <v>922</v>
+      </c>
+      <c r="L73" t="n">
+        <v>115</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:11.711</t>
+          <t>2026-05-29 09:47:33.734</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779509286977</v>
+        <v>1780022852303</v>
       </c>
       <c r="C74" t="n">
-        <v>87370</v>
+        <v>76621</v>
       </c>
       <c r="D74" t="n">
-        <v>-276.24</v>
+        <v>-1328.76</v>
       </c>
       <c r="E74" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F74" t="n">
-        <v>826</v>
+        <v>7375</v>
       </c>
       <c r="G74" t="n">
-        <v>98.31</v>
+        <v>368.83</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1429</v>
+      </c>
+      <c r="L74" t="n">
+        <v>108</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.386</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:11.732</t>
+          <t>2026-05-29 09:47:33.735</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779509287178</v>
+        <v>1780022852503</v>
       </c>
       <c r="C75" t="n">
-        <v>87537</v>
+        <v>76446</v>
       </c>
       <c r="D75" t="n">
-        <v>-95.43000000000001</v>
+        <v>-1437.32</v>
       </c>
       <c r="E75" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F75" t="n">
-        <v>563</v>
+        <v>7375</v>
       </c>
       <c r="G75" t="n">
-        <v>109.52</v>
+        <v>368.83</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L75" t="n">
+        <v>115</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.624</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:11.747</t>
+          <t>2026-05-29 09:47:34.112</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779509287380</v>
+        <v>1780022852722</v>
       </c>
       <c r="C76" t="n">
-        <v>87340</v>
+        <v>76418</v>
       </c>
       <c r="D76" t="n">
-        <v>-287.66</v>
+        <v>-1393.45</v>
       </c>
       <c r="E76" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F76" t="n">
-        <v>563</v>
+        <v>7375</v>
       </c>
       <c r="G76" t="n">
-        <v>109.52</v>
+        <v>368.83</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1388</v>
+      </c>
+      <c r="L76" t="n">
+        <v>108</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:11.963</t>
+          <t>2026-05-29 09:47:34.122</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779509287581</v>
+        <v>1780022852922</v>
       </c>
       <c r="C77" t="n">
-        <v>87440</v>
+        <v>76387</v>
       </c>
       <c r="D77" t="n">
-        <v>-173.28</v>
+        <v>-1354.78</v>
       </c>
       <c r="E77" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F77" t="n">
-        <v>563</v>
+        <v>7375</v>
       </c>
       <c r="G77" t="n">
-        <v>109.52</v>
+        <v>368.83</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1199</v>
+      </c>
+      <c r="L77" t="n">
+        <v>113</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:11.991</t>
+          <t>2026-05-29 09:47:34.150</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779509287783</v>
+        <v>1780022853122</v>
       </c>
       <c r="C78" t="n">
-        <v>87577</v>
+        <v>76361</v>
       </c>
       <c r="D78" t="n">
-        <v>-27.61</v>
+        <v>-1313.04</v>
       </c>
       <c r="E78" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F78" t="n">
-        <v>563</v>
+        <v>7375</v>
       </c>
       <c r="G78" t="n">
-        <v>109.52</v>
+        <v>368.83</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1028</v>
+      </c>
+      <c r="L78" t="n">
+        <v>107</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.623</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:12.543</t>
+          <t>2026-05-29 09:47:34.420</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779509287984</v>
+        <v>1780022853322</v>
       </c>
       <c r="C79" t="n">
-        <v>87735</v>
+        <v>76262</v>
       </c>
       <c r="D79" t="n">
-        <v>131.77</v>
+        <v>-1346.39</v>
       </c>
       <c r="E79" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F79" t="n">
-        <v>645</v>
+        <v>7375</v>
       </c>
       <c r="G79" t="n">
-        <v>110.46</v>
+        <v>368.83</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1097</v>
+      </c>
+      <c r="L79" t="n">
+        <v>117</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.133</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:12.815</t>
+          <t>2026-05-29 09:47:34.421</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779509288185</v>
+        <v>1780022853522</v>
       </c>
       <c r="C80" t="n">
-        <v>87336</v>
+        <v>76178</v>
       </c>
       <c r="D80" t="n">
-        <v>-273.82</v>
+        <v>-1363.07</v>
       </c>
       <c r="E80" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F80" t="n">
-        <v>645</v>
+        <v>7375</v>
       </c>
       <c r="G80" t="n">
-        <v>110.46</v>
+        <v>368.83</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K80" t="n">
+        <v>899</v>
+      </c>
+      <c r="L80" t="n">
+        <v>116</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:12.817</t>
+          <t>2026-05-29 09:47:35.392</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779509288387</v>
+        <v>1780022853723</v>
       </c>
       <c r="C81" t="n">
-        <v>87474</v>
+        <v>76172</v>
       </c>
       <c r="D81" t="n">
-        <v>-122.13</v>
+        <v>-1300.92</v>
       </c>
       <c r="E81" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F81" t="n">
-        <v>645</v>
+        <v>7375</v>
       </c>
       <c r="G81" t="n">
-        <v>110.46</v>
+        <v>368.83</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1668</v>
+      </c>
+      <c r="L81" t="n">
+        <v>108</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.888</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:12.818</t>
+          <t>2026-05-29 09:47:35.393</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779509288588</v>
+        <v>1780022853922</v>
       </c>
       <c r="C82" t="n">
-        <v>87596</v>
+        <v>76234</v>
       </c>
       <c r="D82" t="n">
-        <v>5.98</v>
+        <v>-1173.87</v>
       </c>
       <c r="E82" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F82" t="n">
-        <v>645</v>
+        <v>7375</v>
       </c>
       <c r="G82" t="n">
-        <v>110.46</v>
+        <v>368.83</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1470</v>
+      </c>
+      <c r="L82" t="n">
+        <v>122</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.915</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:13.150</t>
+          <t>2026-05-29 09:47:35.715</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779509288789</v>
+        <v>1780022854123</v>
       </c>
       <c r="C83" t="n">
-        <v>87589</v>
+        <v>75979</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.32</v>
+        <v>-1370.18</v>
       </c>
       <c r="E83" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F83" t="n">
-        <v>785</v>
+        <v>7375</v>
       </c>
       <c r="G83" t="n">
-        <v>113.98</v>
+        <v>368.83</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1591</v>
+      </c>
+      <c r="L83" t="n">
+        <v>150</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.022</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:13.414</t>
+          <t>2026-05-29 09:47:35.717</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779509288991</v>
+        <v>1780022854341</v>
       </c>
       <c r="C84" t="n">
-        <v>87556</v>
+        <v>75992</v>
       </c>
       <c r="D84" t="n">
-        <v>-34.26</v>
+        <v>-1288.67</v>
       </c>
       <c r="E84" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F84" t="n">
-        <v>785</v>
+        <v>7375</v>
       </c>
       <c r="G84" t="n">
-        <v>113.98</v>
+        <v>368.83</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L84" t="n">
+        <v>119</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.667</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:13.452</t>
+          <t>2026-05-29 09:47:35.719</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779509289192</v>
+        <v>1780022854541</v>
       </c>
       <c r="C85" t="n">
-        <v>87682</v>
+        <v>75877</v>
       </c>
       <c r="D85" t="n">
-        <v>93.45999999999999</v>
+        <v>-1339.23</v>
       </c>
       <c r="E85" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F85" t="n">
-        <v>785</v>
+        <v>7375</v>
       </c>
       <c r="G85" t="n">
-        <v>113.98</v>
+        <v>368.83</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1176</v>
+      </c>
+      <c r="L85" t="n">
+        <v>108</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.188</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:13.707</t>
+          <t>2026-05-29 09:47:35.720</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779509289393</v>
+        <v>1780022854741</v>
       </c>
       <c r="C86" t="n">
-        <v>87741</v>
+        <v>75834</v>
       </c>
       <c r="D86" t="n">
-        <v>147.78</v>
+        <v>-1315.27</v>
       </c>
       <c r="E86" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F86" t="n">
-        <v>644</v>
+        <v>7375</v>
       </c>
       <c r="G86" t="n">
-        <v>115.26</v>
+        <v>368.83</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K86" t="n">
+        <v>978</v>
+      </c>
+      <c r="L86" t="n">
+        <v>109</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.061</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:13.714</t>
+          <t>2026-05-29 09:47:36.151</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779509289595</v>
+        <v>1780022854942</v>
       </c>
       <c r="C87" t="n">
-        <v>87408</v>
+        <v>75609</v>
       </c>
       <c r="D87" t="n">
-        <v>-192.61</v>
+        <v>-1474.51</v>
       </c>
       <c r="E87" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F87" t="n">
-        <v>644</v>
+        <v>7375</v>
       </c>
       <c r="G87" t="n">
-        <v>115.26</v>
+        <v>368.83</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1208</v>
+      </c>
+      <c r="L87" t="n">
+        <v>108</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.905</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:13.976</t>
+          <t>2026-05-29 09:47:36.153</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779509289796</v>
+        <v>1780022855141</v>
       </c>
       <c r="C88" t="n">
-        <v>87544</v>
+        <v>75564</v>
       </c>
       <c r="D88" t="n">
-        <v>-46.98</v>
+        <v>-1445.78</v>
       </c>
       <c r="E88" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F88" t="n">
-        <v>644</v>
+        <v>7375</v>
       </c>
       <c r="G88" t="n">
-        <v>115.26</v>
+        <v>368.83</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1011</v>
+      </c>
+      <c r="L88" t="n">
+        <v>119</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.446</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:14.241</t>
+          <t>2026-05-29 09:47:36.498</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779509289997</v>
+        <v>1780022855341</v>
       </c>
       <c r="C89" t="n">
-        <v>87734</v>
+        <v>75692</v>
       </c>
       <c r="D89" t="n">
-        <v>145.37</v>
+        <v>-1245.49</v>
       </c>
       <c r="E89" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F89" t="n">
-        <v>644</v>
+        <v>7375</v>
       </c>
       <c r="G89" t="n">
-        <v>115.26</v>
+        <v>368.83</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1155</v>
+      </c>
+      <c r="L89" t="n">
+        <v>122</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.279</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:14.569</t>
+          <t>2026-05-29 09:47:36.517</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779509290199</v>
+        <v>1780022855541</v>
       </c>
       <c r="C90" t="n">
-        <v>87380</v>
+        <v>76034</v>
       </c>
       <c r="D90" t="n">
-        <v>-215.9</v>
+        <v>-841.22</v>
       </c>
       <c r="E90" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F90" t="n">
-        <v>766</v>
+        <v>4058</v>
       </c>
       <c r="G90" t="n">
-        <v>114.34</v>
+        <v>368.83</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K90" t="n">
+        <v>975</v>
+      </c>
+      <c r="L90" t="n">
+        <v>111</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.888</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:14.842</t>
+          <t>2026-05-29 09:47:37.321</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779509290400</v>
+        <v>1780022855760</v>
       </c>
       <c r="C91" t="n">
-        <v>87449</v>
+        <v>76271</v>
       </c>
       <c r="D91" t="n">
-        <v>-136.1</v>
+        <v>-562.16</v>
       </c>
       <c r="E91" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F91" t="n">
-        <v>766</v>
+        <v>4058</v>
       </c>
       <c r="G91" t="n">
-        <v>114.34</v>
+        <v>368.83</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1560</v>
+      </c>
+      <c r="L91" t="n">
+        <v>113</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.134</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:14.844</t>
+          <t>2026-05-29 09:47:37.324</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779509290602</v>
+        <v>1780022855960</v>
       </c>
       <c r="C92" t="n">
-        <v>87434</v>
+        <v>76327</v>
       </c>
       <c r="D92" t="n">
-        <v>-144.3</v>
+        <v>-478.05</v>
       </c>
       <c r="E92" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F92" t="n">
-        <v>766</v>
+        <v>4058</v>
       </c>
       <c r="G92" t="n">
-        <v>114.34</v>
+        <v>368.83</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1362</v>
+      </c>
+      <c r="L92" t="n">
+        <v>115</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.428</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:15.108</t>
+          <t>2026-05-29 09:47:37.325</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779509290803</v>
+        <v>1780022856160</v>
       </c>
       <c r="C93" t="n">
-        <v>87580</v>
+        <v>76401</v>
       </c>
       <c r="D93" t="n">
-        <v>8.92</v>
+        <v>-380.15</v>
       </c>
       <c r="E93" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F93" t="n">
-        <v>785</v>
+        <v>4058</v>
       </c>
       <c r="G93" t="n">
-        <v>112.63</v>
+        <v>368.83</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1164</v>
+      </c>
+      <c r="L93" t="n">
+        <v>95</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.197</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:15.109</t>
+          <t>2026-05-29 09:47:38.034</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779509291004</v>
+        <v>1780022856360</v>
       </c>
       <c r="C94" t="n">
-        <v>87633</v>
+        <v>76317</v>
       </c>
       <c r="D94" t="n">
-        <v>61.47</v>
+        <v>-445.14</v>
       </c>
       <c r="E94" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F94" t="n">
-        <v>785</v>
+        <v>4058</v>
       </c>
       <c r="G94" t="n">
-        <v>112.63</v>
+        <v>368.83</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1673</v>
+      </c>
+      <c r="L94" t="n">
+        <v>112</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:15.110</t>
+          <t>2026-05-29 09:47:38.035</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779509291206</v>
+        <v>1780022856560</v>
       </c>
       <c r="C95" t="n">
-        <v>87534</v>
+        <v>76293</v>
       </c>
       <c r="D95" t="n">
-        <v>-40.6</v>
+        <v>-446.88</v>
       </c>
       <c r="E95" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F95" t="n">
-        <v>785</v>
+        <v>4058</v>
       </c>
       <c r="G95" t="n">
-        <v>112.63</v>
+        <v>368.83</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1474</v>
+      </c>
+      <c r="L95" t="n">
+        <v>107</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.072</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:15.750</t>
+          <t>2026-05-29 09:47:38.037</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779509291407</v>
+        <v>1780022856760</v>
       </c>
       <c r="C96" t="n">
-        <v>88349</v>
+        <v>76372</v>
       </c>
       <c r="D96" t="n">
-        <v>776.4299999999999</v>
+        <v>-345.54</v>
       </c>
       <c r="E96" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F96" t="n">
-        <v>785</v>
+        <v>4058</v>
       </c>
       <c r="G96" t="n">
-        <v>112.63</v>
+        <v>368.83</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L96" t="n">
+        <v>112</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:15.990</t>
+          <t>2026-05-29 09:47:38.038</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779509291608</v>
+        <v>1780022856960</v>
       </c>
       <c r="C97" t="n">
-        <v>88326</v>
+        <v>76340</v>
       </c>
       <c r="D97" t="n">
-        <v>714.61</v>
+        <v>-360.26</v>
       </c>
       <c r="E97" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F97" t="n">
-        <v>785</v>
+        <v>1259</v>
       </c>
       <c r="G97" t="n">
-        <v>112.63</v>
+        <v>374.42</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1077</v>
+      </c>
+      <c r="L97" t="n">
+        <v>109</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.293</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:15.991</t>
+          <t>2026-05-29 09:47:38.786</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779509291810</v>
+        <v>1780022857160</v>
       </c>
       <c r="C98" t="n">
-        <v>89059</v>
+        <v>76318</v>
       </c>
       <c r="D98" t="n">
-        <v>1411.88</v>
+        <v>-364.25</v>
       </c>
       <c r="E98" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F98" t="n">
-        <v>785</v>
+        <v>1259</v>
       </c>
       <c r="G98" t="n">
-        <v>112.63</v>
+        <v>374.42</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1625</v>
+      </c>
+      <c r="L98" t="n">
+        <v>112</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.906</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:16.290</t>
+          <t>2026-05-29 09:47:38.787</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779509292011</v>
+        <v>1780022857379</v>
       </c>
       <c r="C99" t="n">
-        <v>88379</v>
+        <v>76334</v>
       </c>
       <c r="D99" t="n">
-        <v>661.28</v>
+        <v>-330.04</v>
       </c>
       <c r="E99" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F99" t="n">
-        <v>785</v>
+        <v>1259</v>
       </c>
       <c r="G99" t="n">
-        <v>112.63</v>
+        <v>374.42</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1408</v>
+      </c>
+      <c r="L99" t="n">
+        <v>111</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.848</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:16.561</t>
+          <t>2026-05-29 09:47:38.789</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779509292212</v>
+        <v>1780022857579</v>
       </c>
       <c r="C100" t="n">
-        <v>88392</v>
+        <v>76390</v>
       </c>
       <c r="D100" t="n">
-        <v>641.22</v>
+        <v>-257.53</v>
       </c>
       <c r="E100" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F100" t="n">
-        <v>785</v>
+        <v>639</v>
       </c>
       <c r="G100" t="n">
-        <v>112.63</v>
+        <v>367.3</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1209</v>
+      </c>
+      <c r="L100" t="n">
+        <v>105</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:16.807</t>
+          <t>2026-05-29 09:47:38.789</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779509292414</v>
+        <v>1780022857779</v>
       </c>
       <c r="C101" t="n">
-        <v>88604</v>
+        <v>76272</v>
       </c>
       <c r="D101" t="n">
-        <v>821.16</v>
+        <v>-362.66</v>
       </c>
       <c r="E101" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F101" t="n">
-        <v>785</v>
+        <v>639</v>
       </c>
       <c r="G101" t="n">
-        <v>112.63</v>
+        <v>367.3</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L101" t="n">
+        <v>112</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.605</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:16.808</t>
+          <t>2026-05-29 09:47:38.956</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779509292615</v>
+        <v>1780022857979</v>
       </c>
       <c r="C102" t="n">
-        <v>88506</v>
+        <v>76196</v>
       </c>
       <c r="D102" t="n">
-        <v>682.1</v>
+        <v>-420.53</v>
       </c>
       <c r="E102" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F102" t="n">
-        <v>1712</v>
+        <v>639</v>
       </c>
       <c r="G102" t="n">
-        <v>112.63</v>
+        <v>367.3</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K102" t="n">
+        <v>976</v>
+      </c>
+      <c r="L102" t="n">
+        <v>105</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.702</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:17.088</t>
+          <t>2026-05-29 09:47:39.869</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779509292817</v>
+        <v>1780022858179</v>
       </c>
       <c r="C103" t="n">
-        <v>88558</v>
+        <v>76155</v>
       </c>
       <c r="D103" t="n">
-        <v>700</v>
+        <v>-440.5</v>
       </c>
       <c r="E103" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F103" t="n">
-        <v>1712</v>
+        <v>639</v>
       </c>
       <c r="G103" t="n">
-        <v>112.63</v>
+        <v>367.3</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J103" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1690</v>
+      </c>
+      <c r="L103" t="n">
+        <v>105</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.615</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:17.105</t>
+          <t>2026-05-29 09:47:39.876</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779509293018</v>
+        <v>1780022858379</v>
       </c>
       <c r="C104" t="n">
-        <v>88106</v>
+        <v>76184</v>
       </c>
       <c r="D104" t="n">
-        <v>213</v>
+        <v>-389.47</v>
       </c>
       <c r="E104" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F104" t="n">
-        <v>1712</v>
+        <v>639</v>
       </c>
       <c r="G104" t="n">
-        <v>112.63</v>
+        <v>367.3</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1497</v>
+      </c>
+      <c r="L104" t="n">
+        <v>106</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.495</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:17.446</t>
+          <t>2026-05-29 09:47:39.877</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779509293219</v>
+        <v>1780022858579</v>
       </c>
       <c r="C105" t="n">
-        <v>88330</v>
+        <v>76196</v>
       </c>
       <c r="D105" t="n">
-        <v>426.35</v>
+        <v>-358</v>
       </c>
       <c r="E105" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F105" t="n">
-        <v>1712</v>
+        <v>639</v>
       </c>
       <c r="G105" t="n">
-        <v>112.63</v>
+        <v>367.3</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1298</v>
+      </c>
+      <c r="L105" t="n">
+        <v>105</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.431</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:17.739</t>
+          <t>2026-05-29 09:47:40.396</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779509293421</v>
+        <v>1780022858779</v>
       </c>
       <c r="C106" t="n">
-        <v>88585</v>
+        <v>76175</v>
       </c>
       <c r="D106" t="n">
-        <v>660.03</v>
+        <v>-361.1</v>
       </c>
       <c r="E106" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F106" t="n">
-        <v>1712</v>
+        <v>639</v>
       </c>
       <c r="G106" t="n">
-        <v>112.63</v>
+        <v>367.3</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1616</v>
+      </c>
+      <c r="L106" t="n">
+        <v>105</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:17.994</t>
+          <t>2026-05-29 09:47:40.397</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779509293622</v>
+        <v>1780022858998</v>
       </c>
       <c r="C107" t="n">
-        <v>88799</v>
+        <v>76176</v>
       </c>
       <c r="D107" t="n">
-        <v>841.03</v>
+        <v>-342.05</v>
       </c>
       <c r="E107" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="F107" t="n">
-        <v>986</v>
+        <v>639</v>
       </c>
       <c r="G107" t="n">
-        <v>135.54</v>
+        <v>367.3</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1398</v>
+      </c>
+      <c r="L107" t="n">
+        <v>103</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.436</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:17.995</t>
+          <t>2026-05-29 09:47:40.399</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779509293823</v>
+        <v>1780022859198</v>
       </c>
       <c r="C108" t="n">
-        <v>88407</v>
+        <v>76104</v>
       </c>
       <c r="D108" t="n">
-        <v>406.98</v>
+        <v>-396.94</v>
       </c>
       <c r="E108" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="F108" t="n">
-        <v>986</v>
+        <v>639</v>
       </c>
       <c r="G108" t="n">
-        <v>135.54</v>
+        <v>367.3</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L108" t="n">
+        <v>105</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.307</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:17.999</t>
+          <t>2026-05-29 09:47:40.400</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779509294025</v>
+        <v>1780022859398</v>
       </c>
       <c r="C109" t="n">
-        <v>88497</v>
+        <v>76036</v>
       </c>
       <c r="D109" t="n">
-        <v>476.63</v>
+        <v>-445.1</v>
       </c>
       <c r="E109" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="F109" t="n">
-        <v>986</v>
+        <v>639</v>
       </c>
       <c r="G109" t="n">
-        <v>135.54</v>
+        <v>367.3</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1001</v>
+      </c>
+      <c r="L109" t="n">
+        <v>103</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.888</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:18.258</t>
+          <t>2026-05-29 09:47:43.059</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779509294226</v>
+        <v>1780022859598</v>
       </c>
       <c r="C110" t="n">
-        <v>88863</v>
+        <v>76022</v>
       </c>
       <c r="D110" t="n">
-        <v>818.8</v>
+        <v>-436.84</v>
       </c>
       <c r="E110" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F110" t="n">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="G110" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K110" t="n">
+        <v>3460</v>
+      </c>
+      <c r="L110" t="n">
+        <v>106</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:18.540</t>
+          <t>2026-05-29 09:47:43.060</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779509294427</v>
+        <v>1780022859798</v>
       </c>
       <c r="C111" t="n">
-        <v>88873</v>
+        <v>76024</v>
       </c>
       <c r="D111" t="n">
-        <v>787.86</v>
+        <v>-413</v>
       </c>
       <c r="E111" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F111" t="n">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="G111" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J111" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K111" t="n">
+        <v>3261</v>
+      </c>
+      <c r="L111" t="n">
+        <v>108</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.926</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:18.783</t>
+          <t>2026-05-29 09:47:43.414</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779509294629</v>
+        <v>1780022859998</v>
       </c>
       <c r="C112" t="n">
-        <v>88802</v>
+        <v>76044</v>
       </c>
       <c r="D112" t="n">
-        <v>677.46</v>
+        <v>-372.35</v>
       </c>
       <c r="E112" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F112" t="n">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="G112" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J112" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K112" t="n">
+        <v>3415</v>
+      </c>
+      <c r="L112" t="n">
+        <v>101</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.911</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:18.804</t>
+          <t>2026-05-29 09:47:43.415</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779509294830</v>
+        <v>1780022862338</v>
       </c>
       <c r="C113" t="n">
-        <v>89396</v>
+        <v>75801</v>
       </c>
       <c r="D113" t="n">
-        <v>1237.59</v>
+        <v>-596.73</v>
       </c>
       <c r="E113" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F113" t="n">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="G113" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1076</v>
+      </c>
+      <c r="L113" t="n">
+        <v>112</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.764</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:19.102</t>
+          <t>2026-05-29 09:47:43.418</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779509295031</v>
+        <v>1780022862556</v>
       </c>
       <c r="C114" t="n">
-        <v>90430</v>
+        <v>75824</v>
       </c>
       <c r="D114" t="n">
-        <v>2209.71</v>
+        <v>-543.9</v>
       </c>
       <c r="E114" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F114" t="n">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="G114" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K114" t="n">
+        <v>860</v>
+      </c>
+      <c r="L114" t="n">
+        <v>107</v>
+      </c>
+      <c r="M114" t="n">
+        <v>2.144</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:19.370</t>
+          <t>2026-05-29 09:47:44.531</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779509295233</v>
+        <v>1780022862756</v>
       </c>
       <c r="C115" t="n">
-        <v>90928</v>
+        <v>75809</v>
       </c>
       <c r="D115" t="n">
-        <v>2597.23</v>
+        <v>-531.7</v>
       </c>
       <c r="E115" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F115" t="n">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="G115" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1774</v>
+      </c>
+      <c r="L115" t="n">
+        <v>106</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.217</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:19.777</t>
+          <t>2026-05-29 09:47:44.533</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779509295434</v>
+        <v>1780022862956</v>
       </c>
       <c r="C116" t="n">
-        <v>90654</v>
+        <v>75868</v>
       </c>
       <c r="D116" t="n">
-        <v>2193.36</v>
+        <v>-446.12</v>
       </c>
       <c r="E116" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F116" t="n">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="G116" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1575</v>
+      </c>
+      <c r="L116" t="n">
+        <v>112</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.307</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:20.033</t>
+          <t>2026-05-29 09:47:44.691</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779509295636</v>
+        <v>1780022863156</v>
       </c>
       <c r="C117" t="n">
-        <v>90481</v>
+        <v>75921</v>
       </c>
       <c r="D117" t="n">
-        <v>1910.7</v>
+        <v>-370.81</v>
       </c>
       <c r="E117" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F117" t="n">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="G117" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1534</v>
+      </c>
+      <c r="L117" t="n">
+        <v>107</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.165</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:20.034</t>
+          <t>2026-05-29 09:47:44.772</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779509295837</v>
+        <v>1780022863356</v>
       </c>
       <c r="C118" t="n">
-        <v>90377</v>
+        <v>75979</v>
       </c>
       <c r="D118" t="n">
-        <v>1711.16</v>
+        <v>-294.27</v>
       </c>
       <c r="E118" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F118" t="n">
-        <v>705</v>
+        <v>5737</v>
       </c>
       <c r="G118" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1414</v>
+      </c>
+      <c r="L118" t="n">
+        <v>113</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.179</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:20.299</t>
+          <t>2026-05-29 09:47:44.792</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779509296038</v>
+        <v>1780022863556</v>
       </c>
       <c r="C119" t="n">
-        <v>90416</v>
+        <v>75936</v>
       </c>
       <c r="D119" t="n">
-        <v>1664.6</v>
+        <v>-322.56</v>
       </c>
       <c r="E119" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F119" t="n">
-        <v>705</v>
+        <v>5737</v>
       </c>
       <c r="G119" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1236</v>
+      </c>
+      <c r="L119" t="n">
+        <v>106</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.659</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:20.303</t>
+          <t>2026-05-29 09:47:44.846</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779509296240</v>
+        <v>1780022863775</v>
       </c>
       <c r="C120" t="n">
-        <v>90419</v>
+        <v>75932</v>
       </c>
       <c r="D120" t="n">
-        <v>1584.37</v>
+        <v>-310.43</v>
       </c>
       <c r="E120" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F120" t="n">
-        <v>705</v>
+        <v>5737</v>
       </c>
       <c r="G120" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1070</v>
+      </c>
+      <c r="L120" t="n">
+        <v>110</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:20.573</t>
+          <t>2026-05-29 09:47:45.657</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779509296441</v>
+        <v>1780022863975</v>
       </c>
       <c r="C121" t="n">
-        <v>90534</v>
+        <v>75915</v>
       </c>
       <c r="D121" t="n">
-        <v>1620.15</v>
+        <v>-311.91</v>
       </c>
       <c r="E121" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F121" t="n">
-        <v>705</v>
+        <v>5737</v>
       </c>
       <c r="G121" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1681</v>
+      </c>
+      <c r="L121" t="n">
+        <v>107</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.621</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:20.575</t>
+          <t>2026-05-29 09:47:45.659</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779509296642</v>
+        <v>1780022864175</v>
       </c>
       <c r="C122" t="n">
-        <v>90147</v>
+        <v>75866</v>
       </c>
       <c r="D122" t="n">
-        <v>1152.15</v>
+        <v>-345.31</v>
       </c>
       <c r="E122" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F122" t="n">
-        <v>705</v>
+        <v>5737</v>
       </c>
       <c r="G122" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1483</v>
+      </c>
+      <c r="L122" t="n">
+        <v>116</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.211</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:21.244</t>
+          <t>2026-05-29 09:47:45.661</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779509296844</v>
+        <v>1780022864375</v>
       </c>
       <c r="C123" t="n">
-        <v>89982</v>
+        <v>75978</v>
       </c>
       <c r="D123" t="n">
-        <v>929.54</v>
+        <v>-216.05</v>
       </c>
       <c r="E123" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F123" t="n">
-        <v>705</v>
+        <v>5737</v>
       </c>
       <c r="G123" t="n">
-        <v>121.28</v>
+        <v>367.3</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1284</v>
+      </c>
+      <c r="L123" t="n">
+        <v>103</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.228</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:21.523</t>
+          <t>2026-05-29 09:47:45.664</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779509297045</v>
+        <v>1780022864575</v>
       </c>
       <c r="C124" t="n">
-        <v>90127</v>
+        <v>75969</v>
       </c>
       <c r="D124" t="n">
-        <v>1028.06</v>
+        <v>-214.24</v>
       </c>
       <c r="E124" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F124" t="n">
-        <v>705</v>
+        <v>1299</v>
       </c>
       <c r="G124" t="n">
-        <v>121.28</v>
+        <v>397.41</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1087</v>
+      </c>
+      <c r="L124" t="n">
+        <v>107</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.554</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:21.524</t>
+          <t>2026-05-29 09:47:46.275</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779509297246</v>
+        <v>1780022864775</v>
       </c>
       <c r="C125" t="n">
-        <v>89998</v>
+        <v>75893</v>
       </c>
       <c r="D125" t="n">
-        <v>847.66</v>
+        <v>-279.53</v>
       </c>
       <c r="E125" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F125" t="n">
-        <v>705</v>
+        <v>1299</v>
       </c>
       <c r="G125" t="n">
-        <v>121.28</v>
+        <v>397.41</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1499</v>
+      </c>
+      <c r="L125" t="n">
+        <v>96</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.077</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:21.815</t>
+          <t>2026-05-29 09:47:46.333</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779509297448</v>
+        <v>1780022864975</v>
       </c>
       <c r="C126" t="n">
-        <v>90070</v>
+        <v>75885</v>
       </c>
       <c r="D126" t="n">
-        <v>877.28</v>
+        <v>-273.55</v>
       </c>
       <c r="E126" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F126" t="n">
-        <v>3081</v>
+        <v>1299</v>
       </c>
       <c r="G126" t="n">
-        <v>121.28</v>
+        <v>397.41</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1358</v>
+      </c>
+      <c r="L126" t="n">
+        <v>116</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.866</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:21.816</t>
+          <t>2026-05-29 09:47:46.335</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779509297649</v>
+        <v>1780022865175</v>
       </c>
       <c r="C127" t="n">
-        <v>90247</v>
+        <v>75934</v>
       </c>
       <c r="D127" t="n">
-        <v>1010.41</v>
+        <v>-210.88</v>
       </c>
       <c r="E127" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F127" t="n">
-        <v>3081</v>
+        <v>1299</v>
       </c>
       <c r="G127" t="n">
-        <v>121.28</v>
+        <v>397.41</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L127" t="n">
+        <v>102</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.859</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:21.821</t>
+          <t>2026-05-29 09:47:46.782</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779509297850</v>
+        <v>1780022865394</v>
       </c>
       <c r="C128" t="n">
-        <v>90213</v>
+        <v>76101</v>
       </c>
       <c r="D128" t="n">
-        <v>925.89</v>
+        <v>-33.33</v>
       </c>
       <c r="E128" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F128" t="n">
-        <v>483</v>
+        <v>859</v>
       </c>
       <c r="G128" t="n">
-        <v>143.37</v>
+        <v>380.43</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1387</v>
+      </c>
+      <c r="L128" t="n">
+        <v>114</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.842</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:22.238</t>
+          <t>2026-05-29 09:47:46.802</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779509298052</v>
+        <v>1780022865594</v>
       </c>
       <c r="C129" t="n">
-        <v>89642</v>
+        <v>76091</v>
       </c>
       <c r="D129" t="n">
-        <v>308.6</v>
+        <v>-41.67</v>
       </c>
       <c r="E129" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F129" t="n">
-        <v>483</v>
+        <v>859</v>
       </c>
       <c r="G129" t="n">
-        <v>143.37</v>
+        <v>380.43</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1206</v>
+      </c>
+      <c r="L129" t="n">
+        <v>104</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1.556</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:22.486</t>
+          <t>2026-05-29 09:47:46.816</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779509298253</v>
+        <v>1780022865794</v>
       </c>
       <c r="C130" t="n">
-        <v>89723</v>
+        <v>75977</v>
       </c>
       <c r="D130" t="n">
-        <v>374.17</v>
+        <v>-153.58</v>
       </c>
       <c r="E130" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F130" t="n">
-        <v>483</v>
+        <v>859</v>
       </c>
       <c r="G130" t="n">
-        <v>143.37</v>
+        <v>380.43</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1020</v>
+      </c>
+      <c r="L130" t="n">
+        <v>105</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.857</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:22.790</t>
+          <t>2026-05-29 09:47:46.828</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779509298455</v>
+        <v>1780022865994</v>
       </c>
       <c r="C131" t="n">
-        <v>89973</v>
+        <v>76211</v>
       </c>
       <c r="D131" t="n">
-        <v>605.46</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E131" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F131" t="n">
-        <v>483</v>
+        <v>859</v>
       </c>
       <c r="G131" t="n">
-        <v>143.37</v>
+        <v>380.43</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K131" t="n">
+        <v>833</v>
+      </c>
+      <c r="L131" t="n">
+        <v>98</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.895</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:22.792</t>
+          <t>2026-05-29 09:47:47.091</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779509298656</v>
+        <v>1780022866194</v>
       </c>
       <c r="C132" t="n">
-        <v>89676</v>
+        <v>76323</v>
       </c>
       <c r="D132" t="n">
-        <v>278.19</v>
+        <v>195.69</v>
       </c>
       <c r="E132" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F132" t="n">
-        <v>805</v>
+        <v>740</v>
       </c>
       <c r="G132" t="n">
-        <v>141.77</v>
+        <v>365.36</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K132" t="n">
+        <v>896</v>
+      </c>
+      <c r="L132" t="n">
+        <v>106</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1.137</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:23.503</t>
+          <t>2026-05-29 09:47:47.125</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779509298857</v>
+        <v>1780022866394</v>
       </c>
       <c r="C133" t="n">
-        <v>89571</v>
+        <v>76277</v>
       </c>
       <c r="D133" t="n">
-        <v>159.28</v>
+        <v>139.91</v>
       </c>
       <c r="E133" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F133" t="n">
-        <v>805</v>
+        <v>740</v>
       </c>
       <c r="G133" t="n">
-        <v>141.77</v>
+        <v>365.36</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K133" t="n">
+        <v>730</v>
+      </c>
+      <c r="L133" t="n">
+        <v>104</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.978</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:23.767</t>
+          <t>2026-05-29 09:47:47.702</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779509299059</v>
+        <v>1780022866594</v>
       </c>
       <c r="C134" t="n">
-        <v>89666</v>
+        <v>76169</v>
       </c>
       <c r="D134" t="n">
-        <v>246.31</v>
+        <v>24.91</v>
       </c>
       <c r="E134" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F134" t="n">
-        <v>805</v>
+        <v>740</v>
       </c>
       <c r="G134" t="n">
-        <v>141.77</v>
+        <v>365.36</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1106</v>
+      </c>
+      <c r="L134" t="n">
+        <v>108</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2.082</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:23.779</t>
+          <t>2026-05-29 09:47:48.831</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779509299260</v>
+        <v>1780022866813</v>
       </c>
       <c r="C135" t="n">
-        <v>89494</v>
+        <v>75827</v>
       </c>
       <c r="D135" t="n">
-        <v>62</v>
+        <v>-318.33</v>
       </c>
       <c r="E135" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F135" t="n">
-        <v>805</v>
+        <v>740</v>
       </c>
       <c r="G135" t="n">
-        <v>141.77</v>
+        <v>365.36</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K135" t="n">
+        <v>2017</v>
+      </c>
+      <c r="L135" t="n">
+        <v>106</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.776</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:23.781</t>
+          <t>2026-05-29 09:47:48.832</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779509299461</v>
+        <v>1780022867013</v>
       </c>
       <c r="C136" t="n">
-        <v>89269</v>
+        <v>75757</v>
       </c>
       <c r="D136" t="n">
-        <v>-166.1</v>
+        <v>-372.42</v>
       </c>
       <c r="E136" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F136" t="n">
-        <v>805</v>
+        <v>740</v>
       </c>
       <c r="G136" t="n">
-        <v>141.77</v>
+        <v>365.36</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1818</v>
+      </c>
+      <c r="L136" t="n">
+        <v>106</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.976</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:24.290</t>
+          <t>2026-05-29 09:47:48.847</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779509299663</v>
+        <v>1780022867213</v>
       </c>
       <c r="C137" t="n">
-        <v>89298</v>
+        <v>75678</v>
       </c>
       <c r="D137" t="n">
-        <v>-128.8</v>
+        <v>-432.8</v>
       </c>
       <c r="E137" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F137" t="n">
-        <v>805</v>
+        <v>740</v>
       </c>
       <c r="G137" t="n">
-        <v>141.77</v>
+        <v>365.36</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1632</v>
+      </c>
+      <c r="L137" t="n">
+        <v>105</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.722</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:24.579</t>
+          <t>2026-05-29 09:47:49.041</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779509299864</v>
+        <v>1780022867413</v>
       </c>
       <c r="C138" t="n">
-        <v>89194</v>
+        <v>75944</v>
       </c>
       <c r="D138" t="n">
-        <v>-226.36</v>
+        <v>-145.16</v>
       </c>
       <c r="E138" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F138" t="n">
-        <v>805</v>
+        <v>740</v>
       </c>
       <c r="G138" t="n">
-        <v>141.77</v>
+        <v>365.36</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1627</v>
+      </c>
+      <c r="L138" t="n">
+        <v>111</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.076</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:24.584</t>
+          <t>2026-05-29 09:47:49.098</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779509300065</v>
+        <v>1780022867613</v>
       </c>
       <c r="C139" t="n">
-        <v>88235</v>
+        <v>76479</v>
       </c>
       <c r="D139" t="n">
-        <v>-1174.04</v>
+        <v>397.1</v>
       </c>
       <c r="E139" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F139" t="n">
-        <v>805</v>
+        <v>1499</v>
       </c>
       <c r="G139" t="n">
-        <v>141.77</v>
+        <v>375.99</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:24.608</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>1779509300267</v>
-      </c>
-      <c r="C140" t="n">
-        <v>88567</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-783.34</v>
-      </c>
-      <c r="E140" t="n">
-        <v>85</v>
-      </c>
-      <c r="F140" t="n">
-        <v>805</v>
-      </c>
-      <c r="G140" t="n">
-        <v>141.77</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:25.030</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>1779509300468</v>
-      </c>
-      <c r="C141" t="n">
-        <v>88932</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-379.17</v>
-      </c>
-      <c r="E141" t="n">
-        <v>85</v>
-      </c>
-      <c r="F141" t="n">
-        <v>805</v>
-      </c>
-      <c r="G141" t="n">
-        <v>141.77</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:25.321</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1779509300669</v>
-      </c>
-      <c r="C142" t="n">
-        <v>88431</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-861.21</v>
-      </c>
-      <c r="E142" t="n">
-        <v>85</v>
-      </c>
-      <c r="F142" t="n">
-        <v>805</v>
-      </c>
-      <c r="G142" t="n">
-        <v>141.77</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:25.322</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1779509300871</v>
-      </c>
-      <c r="C143" t="n">
-        <v>88437</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-812.15</v>
-      </c>
-      <c r="E143" t="n">
-        <v>85</v>
-      </c>
-      <c r="F143" t="n">
-        <v>805</v>
-      </c>
-      <c r="G143" t="n">
-        <v>141.77</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:25.323</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>1779509301072</v>
-      </c>
-      <c r="C144" t="n">
-        <v>88994</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-214.54</v>
-      </c>
-      <c r="E144" t="n">
-        <v>85</v>
-      </c>
-      <c r="F144" t="n">
-        <v>805</v>
-      </c>
-      <c r="G144" t="n">
-        <v>141.77</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:25.568</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1779509301274</v>
-      </c>
-      <c r="C145" t="n">
-        <v>89097</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-100.82</v>
-      </c>
-      <c r="E145" t="n">
-        <v>85</v>
-      </c>
-      <c r="F145" t="n">
-        <v>2598</v>
-      </c>
-      <c r="G145" t="n">
-        <v>141.77</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:25.569</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1779509301475</v>
-      </c>
-      <c r="C146" t="n">
-        <v>88458</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-734.78</v>
-      </c>
-      <c r="E146" t="n">
-        <v>85</v>
-      </c>
-      <c r="F146" t="n">
-        <v>2598</v>
-      </c>
-      <c r="G146" t="n">
-        <v>141.77</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:25.840</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1779509301676</v>
-      </c>
-      <c r="C147" t="n">
-        <v>89488</v>
-      </c>
-      <c r="D147" t="n">
-        <v>331.96</v>
-      </c>
-      <c r="E147" t="n">
-        <v>85</v>
-      </c>
-      <c r="F147" t="n">
-        <v>2598</v>
-      </c>
-      <c r="G147" t="n">
-        <v>141.77</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:26.140</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>1779509301878</v>
-      </c>
-      <c r="C148" t="n">
-        <v>88523</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-649.64</v>
-      </c>
-      <c r="E148" t="n">
-        <v>92</v>
-      </c>
-      <c r="F148" t="n">
-        <v>684</v>
-      </c>
-      <c r="G148" t="n">
-        <v>132.02</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:26.746</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1779509302079</v>
-      </c>
-      <c r="C149" t="n">
-        <v>88534</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-606.15</v>
-      </c>
-      <c r="E149" t="n">
-        <v>92</v>
-      </c>
-      <c r="F149" t="n">
-        <v>684</v>
-      </c>
-      <c r="G149" t="n">
-        <v>132.02</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:26.747</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1779509302280</v>
-      </c>
-      <c r="C150" t="n">
-        <v>88213</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-896.85</v>
-      </c>
-      <c r="E150" t="n">
-        <v>92</v>
-      </c>
-      <c r="F150" t="n">
-        <v>684</v>
-      </c>
-      <c r="G150" t="n">
-        <v>132.02</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:26.757</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1779509302482</v>
-      </c>
-      <c r="C151" t="n">
-        <v>88370</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-695</v>
-      </c>
-      <c r="E151" t="n">
-        <v>92</v>
-      </c>
-      <c r="F151" t="n">
-        <v>684</v>
-      </c>
-      <c r="G151" t="n">
-        <v>132.02</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:26.812</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1779509302683</v>
-      </c>
-      <c r="C152" t="n">
-        <v>88388</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-642.25</v>
-      </c>
-      <c r="E152" t="n">
-        <v>92</v>
-      </c>
-      <c r="F152" t="n">
-        <v>684</v>
-      </c>
-      <c r="G152" t="n">
-        <v>132.02</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:27.088</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>1779509302884</v>
-      </c>
-      <c r="C153" t="n">
-        <v>88057</v>
-      </c>
-      <c r="D153" t="n">
-        <v>-941.14</v>
-      </c>
-      <c r="E153" t="n">
-        <v>92</v>
-      </c>
-      <c r="F153" t="n">
-        <v>684</v>
-      </c>
-      <c r="G153" t="n">
-        <v>132.02</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I139" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1484</v>
+      </c>
+      <c r="L139" t="n">
+        <v>112</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.953</v>
       </c>
     </row>
   </sheetData>
